--- a/E/SWATMT.xlsx
+++ b/E/SWATMT.xlsx
@@ -11,24 +11,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="5">
   <si>
     <t/>
   </si>
   <si>
-    <t>20142672</t>
+    <t>20070800</t>
   </si>
   <si>
-    <t>DJARUM BLCK MTCHA 12</t>
+    <t>PEMBAYARAN SHOPEE</t>
   </si>
   <si>
     <t>SWATMT</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>RT</t>
   </si>
 </sst>
 </file>
@@ -425,10 +422,10 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -451,7 +448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -466,9 +463,6 @@
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
